--- a/data/trans_orig/P36B13_R-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/P36B13_R-Habitat-trans_orig.xlsx
@@ -731,12 +731,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>72724</t>
+          <t>74649</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>107302</t>
+          <t>109651</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -746,12 +746,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>10,84%</t>
+          <t>11,13%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>15,99%</t>
+          <t>16,34%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -766,12 +766,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>49123</t>
+          <t>48370</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>77549</t>
+          <t>76838</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -781,12 +781,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>7,38%</t>
+          <t>7,27%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>11,65%</t>
+          <t>11,54%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -801,12 +801,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>130358</t>
+          <t>129463</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>174206</t>
+          <t>175992</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -816,12 +816,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>9,75%</t>
+          <t>9,69%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>13,03%</t>
+          <t>13,17%</t>
         </is>
       </c>
     </row>
@@ -844,12 +844,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>563635</t>
+          <t>561286</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>598213</t>
+          <t>596288</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -859,12 +859,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>84,01%</t>
+          <t>83,66%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>89,16%</t>
+          <t>88,87%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -879,12 +879,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>588031</t>
+          <t>588742</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>616457</t>
+          <t>617210</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -894,12 +894,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>88,35%</t>
+          <t>88,46%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>92,62%</t>
+          <t>92,73%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -914,12 +914,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1162311</t>
+          <t>1160525</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1206159</t>
+          <t>1207054</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -929,12 +929,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>86,97%</t>
+          <t>86,83%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>90,25%</t>
+          <t>90,31%</t>
         </is>
       </c>
     </row>
@@ -1074,12 +1074,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>107135</t>
+          <t>109559</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>152473</t>
+          <t>150644</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1089,12 +1089,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>10,52%</t>
+          <t>10,76%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>14,98%</t>
+          <t>14,8%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>71012</t>
+          <t>73193</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>108408</t>
+          <t>107614</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1124,12 +1124,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>6,82%</t>
+          <t>7,03%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>10,41%</t>
+          <t>10,33%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1144,12 +1144,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>190345</t>
+          <t>188976</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>247507</t>
+          <t>245969</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1159,12 +1159,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>9,24%</t>
+          <t>9,18%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>12,02%</t>
+          <t>11,94%</t>
         </is>
       </c>
     </row>
@@ -1187,12 +1187,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>865491</t>
+          <t>867320</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>910829</t>
+          <t>908405</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1202,12 +1202,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>85,02%</t>
+          <t>85,2%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>89,48%</t>
+          <t>89,24%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1222,12 +1222,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>933163</t>
+          <t>933957</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>970559</t>
+          <t>968378</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1237,12 +1237,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>89,59%</t>
+          <t>89,67%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>93,18%</t>
+          <t>92,97%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1257,12 +1257,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1812028</t>
+          <t>1813566</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1869190</t>
+          <t>1870559</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1272,12 +1272,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>87,98%</t>
+          <t>88,06%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>90,76%</t>
+          <t>90,82%</t>
         </is>
       </c>
     </row>
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>82876</t>
+          <t>81072</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>120198</t>
+          <t>119148</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1432,12 +1432,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>10,95%</t>
+          <t>10,71%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>15,88%</t>
+          <t>15,75%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1452,12 +1452,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>42360</t>
+          <t>42801</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>71345</t>
+          <t>71502</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1467,12 +1467,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>5,41%</t>
+          <t>5,47%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>9,12%</t>
+          <t>9,14%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1487,12 +1487,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>129707</t>
+          <t>131382</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>179616</t>
+          <t>179857</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1502,12 +1502,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>8,43%</t>
+          <t>8,54%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>11,67%</t>
+          <t>11,69%</t>
         </is>
       </c>
     </row>
@@ -1530,12 +1530,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>636481</t>
+          <t>637531</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>673803</t>
+          <t>675607</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1545,12 +1545,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>84,12%</t>
+          <t>84,25%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>89,05%</t>
+          <t>89,29%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1565,12 +1565,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>711075</t>
+          <t>710918</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>740060</t>
+          <t>739619</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1580,12 +1580,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>90,88%</t>
+          <t>90,86%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>94,59%</t>
+          <t>94,53%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1600,12 +1600,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1359483</t>
+          <t>1359242</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1409392</t>
+          <t>1407717</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1615,12 +1615,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>88,33%</t>
+          <t>88,31%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>91,57%</t>
+          <t>91,46%</t>
         </is>
       </c>
     </row>
@@ -1760,12 +1760,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>83720</t>
+          <t>84571</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>125061</t>
+          <t>122021</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1775,12 +1775,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>9,02%</t>
+          <t>9,11%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>13,47%</t>
+          <t>13,15%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1795,12 +1795,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>55059</t>
+          <t>55183</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>87462</t>
+          <t>87792</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1810,12 +1810,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>5,34%</t>
+          <t>5,35%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>8,48%</t>
+          <t>8,51%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1830,12 +1830,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>148918</t>
+          <t>148657</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>198235</t>
+          <t>200833</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1845,12 +1845,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>7,6%</t>
+          <t>7,59%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>10,12%</t>
+          <t>10,25%</t>
         </is>
       </c>
     </row>
@@ -1873,12 +1873,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>803124</t>
+          <t>806164</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>844465</t>
+          <t>843614</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1888,12 +1888,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>86,53%</t>
+          <t>86,85%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>90,98%</t>
+          <t>90,89%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1908,12 +1908,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>944112</t>
+          <t>943782</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>976515</t>
+          <t>976391</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1923,12 +1923,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>91,52%</t>
+          <t>91,49%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>94,66%</t>
+          <t>94,65%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1943,12 +1943,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1761524</t>
+          <t>1758926</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1810841</t>
+          <t>1811102</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1958,12 +1958,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>89,88%</t>
+          <t>89,75%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>92,4%</t>
+          <t>92,41%</t>
         </is>
       </c>
     </row>
@@ -2103,12 +2103,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>383818</t>
+          <t>385296</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>460533</t>
+          <t>460979</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2118,12 +2118,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>11,38%</t>
+          <t>11,42%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>13,65%</t>
+          <t>13,66%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2138,12 +2138,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>247534</t>
+          <t>246674</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>310290</t>
+          <t>307483</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2153,12 +2153,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>7,03%</t>
+          <t>7,01%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>8,81%</t>
+          <t>8,73%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2173,12 +2173,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>651834</t>
+          <t>647309</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>748461</t>
+          <t>745995</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2188,12 +2188,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>9,45%</t>
+          <t>9,39%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>10,86%</t>
+          <t>10,82%</t>
         </is>
       </c>
     </row>
@@ -2216,12 +2216,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2913232</t>
+          <t>2912786</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>2989947</t>
+          <t>2988469</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2231,12 +2231,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>86,35%</t>
+          <t>86,34%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>88,62%</t>
+          <t>88,58%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2251,12 +2251,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>3210856</t>
+          <t>3213663</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>3273612</t>
+          <t>3274472</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2266,12 +2266,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>91,19%</t>
+          <t>91,27%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>92,97%</t>
+          <t>92,99%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2286,12 +2286,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>6146450</t>
+          <t>6148916</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>6243077</t>
+          <t>6247602</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2301,12 +2301,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>89,14%</t>
+          <t>89,18%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>90,55%</t>
+          <t>90,61%</t>
         </is>
       </c>
     </row>
@@ -2673,32 +2673,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>28547</t>
+          <t>34692</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>18326</t>
+          <t>22632</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>43949</t>
+          <t>52136</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>4,51%</t>
+          <t>5,04%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2,89%</t>
+          <t>3,29%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>6,94%</t>
+          <t>7,57%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2708,32 +2708,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>22576</t>
+          <t>24607</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>15456</t>
+          <t>16510</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>31738</t>
+          <t>35374</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>3,35%</t>
+          <t>3,37%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>2,3%</t>
+          <t>2,26%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>4,72%</t>
+          <t>4,84%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2743,32 +2743,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>51124</t>
+          <t>59299</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>38491</t>
+          <t>44907</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>67449</t>
+          <t>78166</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>3,91%</t>
+          <t>4,18%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>2,95%</t>
+          <t>3,17%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>5,16%</t>
+          <t>5,51%</t>
         </is>
       </c>
     </row>
@@ -2786,32 +2786,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>604584</t>
+          <t>653735</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>589182</t>
+          <t>636291</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>614805</t>
+          <t>665795</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>95,49%</t>
+          <t>94,96%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>93,06%</t>
+          <t>92,43%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>97,11%</t>
+          <t>96,71%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2821,32 +2821,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>650555</t>
+          <t>705760</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>641393</t>
+          <t>694993</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>657675</t>
+          <t>713857</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>96,65%</t>
+          <t>96,63%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>95,28%</t>
+          <t>95,16%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>97,7%</t>
+          <t>97,74%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2856,32 +2856,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>1255138</t>
+          <t>1359495</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1238813</t>
+          <t>1340628</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1267771</t>
+          <t>1373887</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>96,09%</t>
+          <t>95,82%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>94,84%</t>
+          <t>94,49%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>97,05%</t>
+          <t>96,83%</t>
         </is>
       </c>
     </row>
@@ -2899,17 +2899,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>633131</t>
+          <t>688427</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>633131</t>
+          <t>688427</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>633131</t>
+          <t>688427</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -2934,17 +2934,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>673131</t>
+          <t>730367</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>673131</t>
+          <t>730367</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>673131</t>
+          <t>730367</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -2969,17 +2969,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>1306262</t>
+          <t>1418794</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>1306262</t>
+          <t>1418794</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>1306262</t>
+          <t>1418794</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -3016,32 +3016,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>311371</t>
+          <t>75201</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>76717</t>
+          <t>55999</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>786494</t>
+          <t>97997</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>26,12%</t>
+          <t>7,18%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>6,44%</t>
+          <t>5,34%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>65,98%</t>
+          <t>9,35%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3051,32 +3051,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>29324</t>
+          <t>31920</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>21872</t>
+          <t>21954</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>41063</t>
+          <t>44825</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>3,07%</t>
+          <t>2,99%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>2,29%</t>
+          <t>2,05%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>4,29%</t>
+          <t>4,19%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3086,32 +3086,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>340695</t>
+          <t>107122</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>99914</t>
+          <t>85350</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>971087</t>
+          <t>132654</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>15,86%</t>
+          <t>5,06%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>4,65%</t>
+          <t>4,03%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>45,2%</t>
+          <t>6,27%</t>
         </is>
       </c>
     </row>
@@ -3129,32 +3129,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>880656</t>
+          <t>972851</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>405533</t>
+          <t>950055</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1115310</t>
+          <t>992053</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>73,88%</t>
+          <t>92,82%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>34,02%</t>
+          <t>90,65%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>93,56%</t>
+          <t>94,66%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3164,32 +3164,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>927002</t>
+          <t>1037148</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>915263</t>
+          <t>1024243</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>934454</t>
+          <t>1047114</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>96,93%</t>
+          <t>97,01%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>95,71%</t>
+          <t>95,81%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>97,71%</t>
+          <t>97,95%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3199,32 +3199,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>1807658</t>
+          <t>2009999</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1177266</t>
+          <t>1984467</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>2048439</t>
+          <t>2031771</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>84,14%</t>
+          <t>94,94%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>54,8%</t>
+          <t>93,73%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>95,35%</t>
+          <t>95,97%</t>
         </is>
       </c>
     </row>
@@ -3242,17 +3242,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1192027</t>
+          <t>1048052</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1192027</t>
+          <t>1048052</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1192027</t>
+          <t>1048052</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -3277,17 +3277,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>956326</t>
+          <t>1069068</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>956326</t>
+          <t>1069068</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>956326</t>
+          <t>1069068</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -3312,17 +3312,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>2148353</t>
+          <t>2117121</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>2148353</t>
+          <t>2117121</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>2148353</t>
+          <t>2117121</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -3359,32 +3359,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>51508</t>
+          <t>59626</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>36958</t>
+          <t>43269</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>72342</t>
+          <t>80940</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>7,31%</t>
+          <t>7,42%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>5,24%</t>
+          <t>5,39%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>10,27%</t>
+          <t>10,08%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3394,32 +3394,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>24804</t>
+          <t>30603</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>12187</t>
+          <t>20423</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>41342</t>
+          <t>45570</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>2,66%</t>
+          <t>3,77%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,31%</t>
+          <t>2,52%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>4,43%</t>
+          <t>5,61%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3429,32 +3429,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>76312</t>
+          <t>90230</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>47680</t>
+          <t>71014</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>102470</t>
+          <t>116494</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>4,66%</t>
+          <t>5,59%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>2,91%</t>
+          <t>4,4%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>6,26%</t>
+          <t>7,21%</t>
         </is>
       </c>
     </row>
@@ -3472,32 +3472,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>653172</t>
+          <t>743447</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>632338</t>
+          <t>722133</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>667722</t>
+          <t>759804</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>92,69%</t>
+          <t>92,58%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>89,73%</t>
+          <t>89,92%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>94,76%</t>
+          <t>94,61%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3507,32 +3507,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>907903</t>
+          <t>780973</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>891365</t>
+          <t>766006</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>920520</t>
+          <t>791153</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>97,34%</t>
+          <t>96,23%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>95,57%</t>
+          <t>94,39%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>98,69%</t>
+          <t>97,48%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3542,32 +3542,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>1561076</t>
+          <t>1524419</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1534918</t>
+          <t>1498155</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1589708</t>
+          <t>1543635</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>95,34%</t>
+          <t>94,41%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>93,74%</t>
+          <t>92,79%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>97,09%</t>
+          <t>95,6%</t>
         </is>
       </c>
     </row>
@@ -3585,17 +3585,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>704680</t>
+          <t>803073</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>704680</t>
+          <t>803073</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>704680</t>
+          <t>803073</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -3620,17 +3620,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>932707</t>
+          <t>811576</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>932707</t>
+          <t>811576</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>932707</t>
+          <t>811576</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -3655,17 +3655,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>1637388</t>
+          <t>1614649</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1637388</t>
+          <t>1614649</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1637388</t>
+          <t>1614649</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -3702,32 +3702,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>85835</t>
+          <t>94258</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>68080</t>
+          <t>75037</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>108231</t>
+          <t>118202</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>9,27%</t>
+          <t>9,53%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>7,35%</t>
+          <t>7,59%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>11,69%</t>
+          <t>11,95%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3737,32 +3737,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>49614</t>
+          <t>57245</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>35138</t>
+          <t>43199</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>65429</t>
+          <t>74370</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>4,55%</t>
+          <t>5,14%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>3,22%</t>
+          <t>3,88%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>6,0%</t>
+          <t>6,67%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3772,32 +3772,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>135449</t>
+          <t>151503</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>108820</t>
+          <t>125075</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>161847</t>
+          <t>179864</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>6,72%</t>
+          <t>7,2%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>5,4%</t>
+          <t>5,95%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>8,03%</t>
+          <t>8,55%</t>
         </is>
       </c>
     </row>
@@ -3815,32 +3815,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>839997</t>
+          <t>894869</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>817601</t>
+          <t>870925</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>857752</t>
+          <t>914090</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>90,73%</t>
+          <t>90,47%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>88,31%</t>
+          <t>88,05%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>92,65%</t>
+          <t>92,41%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3850,32 +3850,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>1040755</t>
+          <t>1057304</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>1024940</t>
+          <t>1040179</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>1055231</t>
+          <t>1071350</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>95,45%</t>
+          <t>94,86%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>94,0%</t>
+          <t>93,33%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>96,78%</t>
+          <t>96,12%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3885,32 +3885,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>1880752</t>
+          <t>1952174</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1854354</t>
+          <t>1923813</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1907381</t>
+          <t>1978602</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>93,28%</t>
+          <t>92,8%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>91,97%</t>
+          <t>91,45%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>94,6%</t>
+          <t>94,05%</t>
         </is>
       </c>
     </row>
@@ -3928,17 +3928,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>925832</t>
+          <t>989127</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>925832</t>
+          <t>989127</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>925832</t>
+          <t>989127</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -3963,17 +3963,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>1090369</t>
+          <t>1114549</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>1090369</t>
+          <t>1114549</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>1090369</t>
+          <t>1114549</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -3998,17 +3998,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>2016201</t>
+          <t>2103677</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>2016201</t>
+          <t>2103677</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>2016201</t>
+          <t>2103677</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -4045,32 +4045,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>477261</t>
+          <t>263777</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>240232</t>
+          <t>226688</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>1227438</t>
+          <t>307138</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>13,81%</t>
+          <t>7,48%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>6,95%</t>
+          <t>6,42%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>35,52%</t>
+          <t>8,7%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4080,32 +4080,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>126318</t>
+          <t>144376</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>100023</t>
+          <t>121123</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>150946</t>
+          <t>169961</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>3,46%</t>
+          <t>3,88%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>2,74%</t>
+          <t>3,25%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>4,13%</t>
+          <t>4,56%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4115,32 +4115,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>603580</t>
+          <t>408153</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>356457</t>
+          <t>364422</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>1400988</t>
+          <t>459804</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>8,49%</t>
+          <t>5,63%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>5,01%</t>
+          <t>5,02%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>19,71%</t>
+          <t>6,34%</t>
         </is>
       </c>
     </row>
@@ -4158,32 +4158,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>2978410</t>
+          <t>3264903</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2228233</t>
+          <t>3221542</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3215439</t>
+          <t>3301992</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>86,19%</t>
+          <t>92,52%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>64,48%</t>
+          <t>91,3%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>93,05%</t>
+          <t>93,58%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4193,32 +4193,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>3526216</t>
+          <t>3581184</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>3501588</t>
+          <t>3555599</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>3552511</t>
+          <t>3604437</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>96,54%</t>
+          <t>96,12%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>95,87%</t>
+          <t>95,44%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>97,26%</t>
+          <t>96,75%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4228,32 +4228,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>6504624</t>
+          <t>6846087</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>5707216</t>
+          <t>6794436</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>6751747</t>
+          <t>6889818</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>91,51%</t>
+          <t>94,37%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>80,29%</t>
+          <t>93,66%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>94,99%</t>
+          <t>94,98%</t>
         </is>
       </c>
     </row>
@@ -4271,17 +4271,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>3455671</t>
+          <t>3528680</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>3455671</t>
+          <t>3528680</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>3455671</t>
+          <t>3528680</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -4306,17 +4306,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>3652534</t>
+          <t>3725560</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>3652534</t>
+          <t>3725560</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>3652534</t>
+          <t>3725560</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -4341,17 +4341,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>7108204</t>
+          <t>7254240</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>7108204</t>
+          <t>7254240</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>7108204</t>
+          <t>7254240</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
